--- a/data/backoffice/backoffice.xlsx
+++ b/data/backoffice/backoffice.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/backoffice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{2CC18B3B-0087-44ED-BA23-2179E1418EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{585E3439-9836-429D-A5B9-68191307C7D5}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{2CC18B3B-0087-44ED-BA23-2179E1418EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B17F45D5-C67D-47EF-BCD5-3829E17A3655}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{003DF816-8C03-4A45-B145-3109FB5EBCDE}"/>
   </bookViews>
@@ -77,9 +77,6 @@
     <t>lucas.nogueira@comprint.com.br</t>
   </si>
   <si>
-    <t>joão.silva@comprint.com.br</t>
-  </si>
-  <si>
     <t>vitória.freire@comprint.com.br</t>
   </si>
   <si>
@@ -96,6 +93,9 @@
   </si>
   <si>
     <t>emerson.zanella@comprint.com.br</t>
+  </si>
+  <si>
+    <t>joao.silva@comprint.com.br</t>
   </si>
 </sst>
 </file>
@@ -503,7 +503,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -542,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -556,7 +556,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -567,10 +567,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -581,10 +581,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>

--- a/data/backoffice/backoffice.xlsx
+++ b/data/backoffice/backoffice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/backoffice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{2CC18B3B-0087-44ED-BA23-2179E1418EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B17F45D5-C67D-47EF-BCD5-3829E17A3655}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{2CC18B3B-0087-44ED-BA23-2179E1418EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64AC0775-5421-46EB-94FE-144D52E2C490}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{003DF816-8C03-4A45-B145-3109FB5EBCDE}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{003DF816-8C03-4A45-B145-3109FB5EBCDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -541,6 +541,9 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="1">
+        <v>5511911340912</v>
+      </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
